--- a/Data/Results/Visualizations/INTERCITY/Route_Wise/Madiwala_to_Madhuravoyal/Average/Master_Results.xlsx
+++ b/Data/Results/Visualizations/INTERCITY/Route_Wise/Madiwala_to_Madhuravoyal/Average/Master_Results.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Phase_Difference_Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Descriptive_Statistics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Route_Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Plot_Audit" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF5"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,11 +727,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -751,174 +750,174 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026\PAIR_035_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026\PAIR_042_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13.15565</v>
+        <v>405.7706333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>14.03436666666667</v>
+        <v>325.4048166666667</v>
       </c>
       <c r="I2" t="n">
-        <v>17.5104260598227</v>
+        <v>321.8611957625617</v>
       </c>
       <c r="J2" t="n">
-        <v>17.59592292311513</v>
+        <v>322.4334194047157</v>
       </c>
       <c r="K2" t="n">
-        <v>79.86116714790693</v>
+        <v>64.64531488636605</v>
       </c>
       <c r="L2" t="n">
-        <v>75.22643525442838</v>
+        <v>63.96489623843365</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.878716666666671</v>
+        <v>80.3658166666666</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.08549686329243045</v>
+        <v>-0.5722236421540288</v>
       </c>
       <c r="O2" t="n">
-        <v>4.634731893478545</v>
+        <v>0.6804186479323988</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>20.61666666666668</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>14.51666666666667</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>20.58333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-6.066666666666659</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>0.08215844858586425</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>0.4766783541068861</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-0.3945199055210218</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>29.51666666666667</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>26.68333333333334</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.01643615657683831</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>0.0127297174998127</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>0.00370643907702561</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6.883333333333334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.883333333333334</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.5125712172728395</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>0.4202840859765154</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>0.0922871312963241</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.366666666666667</v>
+        <v>69.25</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.5833333333333334</v>
+        <v>45.56666666666667</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.783333333333334</v>
+        <v>23.68333333333333</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.068290636520454</v>
+        <v>67.11754968426774</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.6703253541496691</v>
+        <v>40.65136137866402</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.397965282370785</v>
+        <v>26.46618830560372</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.683333333333333</v>
+        <v>57.8873</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.35</v>
+        <v>33.78333333333333</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.333333333333333</v>
+        <v>24.10396666666667</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.206663901320678</v>
+        <v>56.35632166455606</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.4473149966220811</v>
+        <v>31.65946275202983</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.759348904698597</v>
+        <v>24.69685891252623</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.105650000000001</v>
+        <v>164.5166666666667</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.10103333333333</v>
+        <v>218.63815</v>
       </c>
       <c r="BC2" t="n">
-        <v>-3.995383333333329</v>
+        <v>-54.12148333333329</v>
       </c>
       <c r="BD2" t="n">
-        <v>12.23547152198156</v>
+        <v>197.6641868309954</v>
       </c>
       <c r="BE2" t="n">
-        <v>16.47828257234338</v>
+        <v>249.2129031164386</v>
       </c>
       <c r="BF2" t="n">
-        <v>-4.242811050361821</v>
+        <v>-51.54871628544322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_043</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -937,174 +936,174 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_036_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_043_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11.71183333333333</v>
+        <v>446.45</v>
       </c>
       <c r="H3" t="n">
-        <v>11.73173333333333</v>
+        <v>341.4423833333333</v>
       </c>
       <c r="I3" t="n">
-        <v>16.43424965629278</v>
+        <v>322.1774743037008</v>
       </c>
       <c r="J3" t="n">
-        <v>16.43868693033036</v>
+        <v>321.6269481176106</v>
       </c>
       <c r="K3" t="n">
-        <v>84.19305084978724</v>
+        <v>64.4401967523076</v>
       </c>
       <c r="L3" t="n">
-        <v>84.07293174806406</v>
+        <v>64.28145295102571</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01989999999999981</v>
+        <v>105.0076166666667</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.004437274037577765</v>
+        <v>0.5505261860902237</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1201191017231764</v>
+        <v>0.1587438012818865</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>41.88333333333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>51.31666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>15.91666666666667</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.2137910036648912</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.4503679422720615</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.2365769386071703</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>32.28333333333333</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>6.316666666666666</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>25.96666666666667</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.0266289259127734</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.06317093999191636</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.03654201407914297</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>7.716666666666667</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-2.300000000000002</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.5319201203612787</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.8996597832386584</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0.3677396628773797</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.683333333333333</v>
+        <v>63.38333333333333</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.1833333333333329</v>
+        <v>6.016666666666673</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.145589159808596</v>
+        <v>67.23521804769611</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.354103498469736</v>
+        <v>58.37602971556508</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.2085143386611401</v>
+        <v>8.859188332131026</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.233333333333333</v>
+        <v>57.93333333333333</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.23205</v>
+        <v>44.56666666666667</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.9987166666666671</v>
+        <v>13.36666666666666</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.726998909362367</v>
+        <v>56.31975683439349</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.895877582706585</v>
+        <v>42.97209112540976</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1.168878673344218</v>
+        <v>13.34766570898373</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.9785</v>
+        <v>164.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.81635</v>
+        <v>181.75905</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.16215</v>
+        <v>-17.15905000000001</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.56166158712181</v>
+        <v>197.7381876113653</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.18870584915403</v>
+        <v>218.8656286111331</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.37295573796778</v>
+        <v>-21.1274409997678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_044</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1123,38 +1122,38 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_037_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_044_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>116.7043666666667</v>
+        <v>408.6267666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>117.7956</v>
+        <v>325.2655</v>
       </c>
       <c r="I4" t="n">
-        <v>106.4407237351212</v>
+        <v>324.4297883243897</v>
       </c>
       <c r="J4" t="n">
-        <v>106.429493371315</v>
+        <v>325.0350667285441</v>
       </c>
       <c r="K4" t="n">
-        <v>57.74313792935574</v>
+        <v>62.28065772239027</v>
       </c>
       <c r="L4" t="n">
-        <v>61.22560386453947</v>
+        <v>63.75914065702941</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.091233333333292</v>
+        <v>83.36126666666661</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01123036380619169</v>
+        <v>-0.6052784041544328</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.482465935183733</v>
+        <v>-1.478482934639139</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.516666666666663</v>
+        <v>76.78333333333333</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1175,298 +1174,1228 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>65.98333333333333</v>
       </c>
       <c r="X4" t="n">
-        <v>13.68333333333333</v>
+        <v>16.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>-13.68333333333333</v>
+        <v>49.08333333333334</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>0.2402194601328752</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1905534317712249</v>
+        <v>0.3478638485950774</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.1905534317712249</v>
+        <v>-0.1076443884622022</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.166666666666667</v>
+        <v>30.53333333333333</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="AE4" t="n">
-        <v>6.166666666666667</v>
+        <v>27.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06082944355873176</v>
+        <v>0.2158637009068103</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>0.0127297174998127</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.06082944355873176</v>
+        <v>0.2031339834069976</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6666666666666666</v>
+        <v>6.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.3333333333333333</v>
+        <v>4</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.07885964335257711</v>
+        <v>0.5924866771054754</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005855051964785372</v>
+        <v>0.4202840859765154</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.07300459138779174</v>
+        <v>0.17220259112896</v>
       </c>
       <c r="AO4" t="n">
-        <v>32.13333333333333</v>
+        <v>75.78333333333333</v>
       </c>
       <c r="AP4" t="n">
-        <v>15.36666666666667</v>
+        <v>46.73333333333333</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16.76666666666666</v>
+        <v>29.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>27.22400876286396</v>
+        <v>70.97085214069388</v>
       </c>
       <c r="AS4" t="n">
-        <v>12.99028801976566</v>
+        <v>41.50209986904579</v>
       </c>
       <c r="AT4" t="n">
-        <v>14.2337207430983</v>
+        <v>29.46875227164809</v>
       </c>
       <c r="AU4" t="n">
-        <v>25.45</v>
+        <v>59.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.98333333333333</v>
+        <v>34.78333333333333</v>
       </c>
       <c r="AW4" t="n">
-        <v>12.46666666666667</v>
+        <v>24.81666666666667</v>
       </c>
       <c r="AX4" t="n">
-        <v>21.71770276874582</v>
+        <v>57.38992771876193</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.46884073038654</v>
+        <v>32.23439151995442</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.24886203835928</v>
+        <v>25.15553619880751</v>
       </c>
       <c r="BA4" t="n">
-        <v>52.2877</v>
+        <v>170.4267666666667</v>
       </c>
       <c r="BB4" t="n">
-        <v>75.42893333333333</v>
+        <v>220.0155</v>
       </c>
       <c r="BC4" t="n">
-        <v>-23.14123333333333</v>
+        <v>-49.58873333333329</v>
       </c>
       <c r="BD4" t="n">
-        <v>57.35932311660007</v>
+        <v>195.0204386267887</v>
       </c>
       <c r="BE4" t="n">
-        <v>81.77395613742682</v>
+        <v>250.5176976874725</v>
       </c>
       <c r="BF4" t="n">
-        <v>-24.41463302082675</v>
+        <v>-55.4972590606838</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_045</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_03-10-2026\PAIR_045_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>446.45</v>
+      </c>
+      <c r="H5" t="n">
+        <v>349.4259833333334</v>
+      </c>
+      <c r="I5" t="n">
+        <v>322.2735940834601</v>
+      </c>
+      <c r="J5" t="n">
+        <v>322.6469826189222</v>
+      </c>
+      <c r="K5" t="n">
+        <v>64.45944316240457</v>
+      </c>
+      <c r="L5" t="n">
+        <v>59.87583735700611</v>
+      </c>
+      <c r="M5" t="n">
+        <v>97.02401666666657</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.3733885354620838</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.583605805398456</v>
+      </c>
+      <c r="P5" t="n">
+        <v>56.61666666666666</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1119717603069536</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1119717603069536</v>
+      </c>
+      <c r="W5" t="n">
+        <v>51.31666666666667</v>
+      </c>
+      <c r="X5" t="n">
+        <v>24.31666666666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.2137910036648912</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.4433224105129225</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.2295314068480313</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>32.28333333333333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>29.61666666666666</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0266289259127734</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.428265735708522</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.4016368097957486</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>7.716666666666667</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>5.683333333333334</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.5621573347884641</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.5110447249900278</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.05111260979843624</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>44.13333333333333</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>25.26666666666667</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>67.30110061302815</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>36.19726417049096</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>31.10383644253719</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>57.93333333333333</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>32.11666666666667</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>25.81666666666666</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>56.31975683439349</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>28.87956171842685</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>27.44019511596664</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>240.5093166666666</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-75.9093166666666</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>197.7381876113653</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>256.1875238587929</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-58.44933624742757</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>46</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_03-10-2026\PAIR_046_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>394.6350333333333</v>
+      </c>
+      <c r="H6" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>324.9350283808783</v>
+      </c>
+      <c r="J6" t="n">
+        <v>325.7263480402497</v>
+      </c>
+      <c r="K6" t="n">
+        <v>64.17415185678969</v>
+      </c>
+      <c r="L6" t="n">
+        <v>63.70255625065911</v>
+      </c>
+      <c r="M6" t="n">
+        <v>64.8850333333333</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.7913196593714247</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4715956061305846</v>
+      </c>
+      <c r="P6" t="n">
+        <v>32.88333333333334</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="W6" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="X6" t="n">
+        <v>20.58333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16.86666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1794253337608642</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.4766783541068861</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.2972530203460219</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>16.01666666666667</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.05059730733317578</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0127297174998127</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.03786758983336308</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.5766516264825126</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.4202840859765154</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.1563675405059972</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>64.65921666666667</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>46.73333333333333</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>17.92588333333334</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>63.80717597571496</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>41.50209986904579</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>22.30507610666917</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>54.06666666666667</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>35.11666666666667</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>54.00426203304914</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>32.50454485672611</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>21.49971717632302</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>176.7758166666667</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>220.4833333333333</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-43.70751666666658</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>206.2279801079839</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>250.8100111568945</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-44.58203104891058</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>48</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>STRICT</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>INTERCITY</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Madiwala to Madhuravoyal</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026\PAIR_038_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>154.2935833333334</v>
-      </c>
-      <c r="H5" t="n">
-        <v>89.89455</v>
-      </c>
-      <c r="I5" t="n">
-        <v>118.6528555237152</v>
-      </c>
-      <c r="J5" t="n">
-        <v>118.3205529638225</v>
-      </c>
-      <c r="K5" t="n">
-        <v>76.62526023529979</v>
-      </c>
-      <c r="L5" t="n">
-        <v>78.97289855535573</v>
-      </c>
-      <c r="M5" t="n">
-        <v>64.39903333333341</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.3323025598927103</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-2.347638320055935</v>
-      </c>
-      <c r="P5" t="n">
-        <v>61.55</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>57.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>57.05</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.09002709918491375</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.09002709918491375</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.1211416233489353</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.1211416233489353</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.3166666666666667</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-0.6833333333333333</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0.01887125568339211</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.03644173622497521</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.0175704805415831</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>19.22816666666667</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>14.0627</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>5.165466666666671</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>21.56383013715203</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>15.34811928295864</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.215710854193391</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>15.13208333333333</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.032083333333331</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>17.72416642729523</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.19959394493595</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.524572482359281</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>58.06666666666667</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>64.73184999999999</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-6.665183333333324</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>79.13481898105066</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>91.736397999703</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-12.60157901865234</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026\PAIR_048_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>410.7333333333333</v>
+      </c>
+      <c r="H7" t="n">
+        <v>348.1472000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>325.3989070955062</v>
+      </c>
+      <c r="J7" t="n">
+        <v>324.8843224200924</v>
+      </c>
+      <c r="K7" t="n">
+        <v>62.04817090988592</v>
+      </c>
+      <c r="L7" t="n">
+        <v>63.51275377345894</v>
+      </c>
+      <c r="M7" t="n">
+        <v>62.58613333333318</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5145846754138006</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.464582863573021</v>
+      </c>
+      <c r="P7" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>65.98333333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>30.58333333333334</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2402194601328752</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.4503679422720615</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.2101484821391863</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>30.53333333333333</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>6.316666666666666</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>24.21666666666667</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.2158637009068103</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.06317093999191636</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1526927609148939</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6.383333333333334</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-3.966666666666666</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.598015576168782</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.9160590253823516</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.3180434492135696</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>76.56666666666666</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.76666666666667</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>71.21683905800106</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>59.81880415688165</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>11.39803490111941</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>59.98333333333333</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>46.88053333333333</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>13.10279999999999</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>57.6088865102048</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>44.25115544180538</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13.35773106839942</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>171.2833333333333</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-12.1166666666667</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>195.5190827900918</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>219.3847649137591</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-23.86568212366731</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>49</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026_to_03-10-2026\PAIR_049_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>407.74795</v>
+      </c>
+      <c r="H8" t="n">
+        <v>346.04665</v>
+      </c>
+      <c r="I8" t="n">
+        <v>323.753642085549</v>
+      </c>
+      <c r="J8" t="n">
+        <v>324.1251397273161</v>
+      </c>
+      <c r="K8" t="n">
+        <v>62.32616891116043</v>
+      </c>
+      <c r="L8" t="n">
+        <v>60.09883681712126</v>
+      </c>
+      <c r="M8" t="n">
+        <v>61.7013</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.3714976417670641</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.22733209403917</v>
+      </c>
+      <c r="P8" t="n">
+        <v>73.21666666666667</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>65.98333333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>20.63333333333333</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>45.35000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.2402194601328752</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.4185697978984132</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.178350337765538</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>30.53333333333333</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>27.86666666666666</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.2158637009068103</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.428265735708522</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.2124020348017117</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>5.016666666666667</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.5924866771054754</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.4666024413592124</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.125884235746263</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>75.51461666666667</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>32.41461666666667</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>70.78420748683264</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>35.97418131675639</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>34.81002617007625</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>59.38333333333333</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>32.11666666666667</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>27.26666666666667</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>57.21717097154523</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>28.82664857731616</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>28.39052239422907</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>170.0333333333333</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>242.5133166666667</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-72.47998333333339</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>194.703693789026</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>258.0108718582774</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-63.30717806925142</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026_to_03-10-2026\PAIR_050_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>420.64665</v>
+      </c>
+      <c r="H9" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>326.4659622430934</v>
+      </c>
+      <c r="J9" t="n">
+        <v>326.1341423944449</v>
+      </c>
+      <c r="K9" t="n">
+        <v>63.92417977688259</v>
+      </c>
+      <c r="L9" t="n">
+        <v>63.01656664035327</v>
+      </c>
+      <c r="M9" t="n">
+        <v>68.89665000000002</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3318198486484789</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9076131365293207</v>
+      </c>
+      <c r="P9" t="n">
+        <v>38.12998333333331</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="W9" t="n">
+        <v>58.16666666666666</v>
+      </c>
+      <c r="X9" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>22.76666666666666</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.3279316256974203</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.4503679422720615</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.1224363165746412</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>21.67998333333333</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6.316666666666666</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>15.36331666666666</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.07129119195051567</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.06317093999191636</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.008120251958599306</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>8.083333333333334</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>10.68333333333333</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-2.599999999999996</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.5879855152386801</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.9301404042363888</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.3421548889977086</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>65.96666666666667</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.1333333333333258</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>64.43671090657982</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>59.92188649758575</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.514824408994066</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>47.53333333333333</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.266666666666666</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>54.47632725636674</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>44.51480319122793</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>9.961524065138811</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>177.1166666666667</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>185.7166666666667</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-8.599999999999994</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>206.4767797507066</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>220.2537734191309</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-13.7769936684243</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>54</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\03-10-2026\PAIR_054_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>417.3654666666667</v>
+      </c>
+      <c r="H10" t="n">
+        <v>352.7333333333333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>324.469507401836</v>
+      </c>
+      <c r="J10" t="n">
+        <v>325.0334484112802</v>
+      </c>
+      <c r="K10" t="n">
+        <v>64.21541291915878</v>
+      </c>
+      <c r="L10" t="n">
+        <v>59.70765591182442</v>
+      </c>
+      <c r="M10" t="n">
+        <v>64.6321333333334</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.5639410094441928</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.507757007334362</v>
+      </c>
+      <c r="P10" t="n">
+        <v>52.86331666666665</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="W10" t="n">
+        <v>58.16666666666666</v>
+      </c>
+      <c r="X10" t="n">
+        <v>24.31666666666667</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>33.84999999999999</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.3279316256974203</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.4423674542915821</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.1144358285941618</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>21.67998333333333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>19.01331666666666</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.1014181648324159</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.428265735708522</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.3268475708761061</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5.683333333333334</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.316666666666666</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.5766516264825126</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.5110447249900278</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.06560690149248471</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>44.46666666666667</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>20.03333333333333</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>63.63085151532849</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>36.40661394018598</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>27.22423757514251</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>53.65215</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>21.20215</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>53.72863846122127</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>29.04782298717766</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>24.68081547404361</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>176.5333333333333</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>243.15</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-66.6166666666667</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>206.0150800117203</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>258.1973335689265</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-52.18225355720622</v>
       </c>
     </row>
   </sheetData>
@@ -1480,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,7 +2457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1537,28 +2466,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1567,28 +2496,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>14.51666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>20.58333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-6.066666666666659</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.08215844858586425</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.4766783541068861</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0.3945199055210218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1597,28 +2526,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>29.51666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>26.68333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.01643615657683831</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.0127297174998127</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.00370643907702561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1627,28 +2556,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>6.883333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2.883333333333334</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.5125712172728395</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.4202840859765154</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.0922871312963241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1657,28 +2586,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.366666666666667</v>
+        <v>69.25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5833333333333334</v>
+        <v>45.56666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>1.783333333333334</v>
+        <v>23.68333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>3.068290636520454</v>
+        <v>67.11754968426774</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6703253541496691</v>
+        <v>40.65136137866402</v>
       </c>
       <c r="H6" t="n">
-        <v>2.397965282370785</v>
+        <v>26.46618830560372</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1687,28 +2616,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.683333333333333</v>
+        <v>57.8873</v>
       </c>
       <c r="D7" t="n">
-        <v>0.35</v>
+        <v>33.78333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>1.333333333333333</v>
+        <v>24.10396666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>2.206663901320678</v>
+        <v>56.35632166455606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4473149966220811</v>
+        <v>31.65946275202983</v>
       </c>
       <c r="H7" t="n">
-        <v>1.759348904698597</v>
+        <v>24.69685891252623</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1717,28 +2646,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.105650000000001</v>
+        <v>164.5166666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>13.10103333333333</v>
+        <v>218.63815</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.995383333333329</v>
+        <v>-54.12148333333329</v>
       </c>
       <c r="F8" t="n">
-        <v>12.23547152198156</v>
+        <v>197.6641868309954</v>
       </c>
       <c r="G8" t="n">
-        <v>16.47828257234338</v>
+        <v>249.2129031164386</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.242811050361821</v>
+        <v>-51.54871628544322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_043</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1747,28 +2676,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_043</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1777,28 +2706,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>51.31666666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>15.91666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.2137910036648912</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.4503679422720615</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0.2365769386071703</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_043</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1807,28 +2736,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>32.28333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>6.316666666666666</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>25.96666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.0266289259127734</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.06317093999191636</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0.03654201407914297</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_043</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1837,28 +2766,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>7.716666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-2.300000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.5319201203612787</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.8996597832386584</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0.3677396628773797</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_043</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1867,28 +2796,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>1.683333333333333</v>
+        <v>63.38333333333333</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1833333333333329</v>
+        <v>6.016666666666673</v>
       </c>
       <c r="F13" t="n">
-        <v>2.145589159808596</v>
+        <v>67.23521804769611</v>
       </c>
       <c r="G13" t="n">
-        <v>2.354103498469736</v>
+        <v>58.37602971556508</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2085143386611401</v>
+        <v>8.859188332131026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_043</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,28 +2826,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.233333333333333</v>
+        <v>57.93333333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>2.23205</v>
+        <v>44.56666666666667</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9987166666666671</v>
+        <v>13.36666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>1.726998909362367</v>
+        <v>56.31975683439349</v>
       </c>
       <c r="G14" t="n">
-        <v>2.895877582706585</v>
+        <v>42.97209112540976</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.168878673344218</v>
+        <v>13.34766570898373</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_036</t>
+          <t>PAIR_043</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1927,28 +2856,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.9785</v>
+        <v>164.6</v>
       </c>
       <c r="D15" t="n">
-        <v>7.81635</v>
+        <v>181.75905</v>
       </c>
       <c r="E15" t="n">
-        <v>1.16215</v>
+        <v>-17.15905000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>12.56166158712181</v>
+        <v>197.7381876113653</v>
       </c>
       <c r="G15" t="n">
-        <v>11.18870584915403</v>
+        <v>218.8656286111331</v>
       </c>
       <c r="H15" t="n">
-        <v>1.37295573796778</v>
+        <v>-21.1274409997678</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_044</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1978,7 +2907,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1987,28 +2916,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>65.98333333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>13.68333333333333</v>
+        <v>16.9</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.68333333333333</v>
+        <v>49.08333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.2402194601328752</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1905534317712249</v>
+        <v>0.3478638485950774</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1905534317712249</v>
+        <v>-0.1076443884622022</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_044</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2017,28 +2946,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.166666666666667</v>
+        <v>30.53333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>6.166666666666667</v>
+        <v>27.7</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06082944355873176</v>
+        <v>0.2158637009068103</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0127297174998127</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06082944355873176</v>
+        <v>0.2031339834069976</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_044</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2047,28 +2976,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6666666666666666</v>
+        <v>6.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3333333333333333</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.3</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07885964335257711</v>
+        <v>0.5924866771054754</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005855051964785372</v>
+        <v>0.4202840859765154</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07300459138779174</v>
+        <v>0.17220259112896</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_044</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2077,28 +3006,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32.13333333333333</v>
+        <v>75.78333333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>15.36666666666667</v>
+        <v>46.73333333333333</v>
       </c>
       <c r="E20" t="n">
-        <v>16.76666666666666</v>
+        <v>29.05</v>
       </c>
       <c r="F20" t="n">
-        <v>27.22400876286396</v>
+        <v>70.97085214069388</v>
       </c>
       <c r="G20" t="n">
-        <v>12.99028801976566</v>
+        <v>41.50209986904579</v>
       </c>
       <c r="H20" t="n">
-        <v>14.2337207430983</v>
+        <v>29.46875227164809</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_044</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2107,28 +3036,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.45</v>
+        <v>59.6</v>
       </c>
       <c r="D21" t="n">
-        <v>12.98333333333333</v>
+        <v>34.78333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>12.46666666666667</v>
+        <v>24.81666666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>21.71770276874582</v>
+        <v>57.38992771876193</v>
       </c>
       <c r="G21" t="n">
-        <v>11.46884073038654</v>
+        <v>32.23439151995442</v>
       </c>
       <c r="H21" t="n">
-        <v>10.24886203835928</v>
+        <v>25.15553619880751</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAIR_037</t>
+          <t>PAIR_044</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2137,28 +3066,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>52.2877</v>
+        <v>170.4267666666667</v>
       </c>
       <c r="D22" t="n">
-        <v>75.42893333333333</v>
+        <v>220.0155</v>
       </c>
       <c r="E22" t="n">
-        <v>-23.14123333333333</v>
+        <v>-49.58873333333329</v>
       </c>
       <c r="F22" t="n">
-        <v>57.35932311660007</v>
+        <v>195.0204386267887</v>
       </c>
       <c r="G22" t="n">
-        <v>81.77395613742682</v>
+        <v>250.5176976874725</v>
       </c>
       <c r="H22" t="n">
-        <v>-24.41463302082675</v>
+        <v>-55.4972590606838</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_045</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,28 +3096,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_045</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2197,28 +3126,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.05</v>
+        <v>51.31666666666667</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>24.31666666666667</v>
       </c>
       <c r="E24" t="n">
-        <v>57.05</v>
+        <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09002709918491375</v>
+        <v>0.2137910036648912</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.4433224105129225</v>
       </c>
       <c r="H24" t="n">
-        <v>0.09002709918491375</v>
+        <v>-0.2295314068480313</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_045</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2227,28 +3156,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.5</v>
+        <v>32.28333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="E25" t="n">
-        <v>4.5</v>
+        <v>29.61666666666666</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1211416233489353</v>
+        <v>0.0266289259127734</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.428265735708522</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1211416233489353</v>
+        <v>-0.4016368097957486</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_045</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2257,28 +3186,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3166666666666667</v>
+        <v>7.716666666666667</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>5.683333333333334</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6833333333333333</v>
+        <v>2.033333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01887125568339211</v>
+        <v>0.5621573347884641</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03644173622497521</v>
+        <v>0.5110447249900278</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0175704805415831</v>
+        <v>0.05111260979843624</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_045</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2287,28 +3216,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19.22816666666667</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>14.0627</v>
+        <v>44.13333333333333</v>
       </c>
       <c r="E27" t="n">
-        <v>5.165466666666671</v>
+        <v>25.26666666666667</v>
       </c>
       <c r="F27" t="n">
-        <v>21.56383013715203</v>
+        <v>67.30110061302815</v>
       </c>
       <c r="G27" t="n">
-        <v>15.34811928295864</v>
+        <v>36.19726417049096</v>
       </c>
       <c r="H27" t="n">
-        <v>6.215710854193391</v>
+        <v>31.10383644253719</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_045</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2317,28 +3246,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.13208333333333</v>
+        <v>57.93333333333333</v>
       </c>
       <c r="D28" t="n">
-        <v>10.1</v>
+        <v>32.11666666666667</v>
       </c>
       <c r="E28" t="n">
-        <v>5.032083333333331</v>
+        <v>25.81666666666666</v>
       </c>
       <c r="F28" t="n">
-        <v>17.72416642729523</v>
+        <v>56.31975683439349</v>
       </c>
       <c r="G28" t="n">
-        <v>11.19959394493595</v>
+        <v>28.87956171842685</v>
       </c>
       <c r="H28" t="n">
-        <v>6.524572482359281</v>
+        <v>27.44019511596664</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_045</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2347,22 +3276,1072 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>58.06666666666667</v>
+        <v>164.6</v>
       </c>
       <c r="D29" t="n">
-        <v>64.73184999999999</v>
+        <v>240.5093166666666</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.665183333333324</v>
+        <v>-75.9093166666666</v>
       </c>
       <c r="F29" t="n">
-        <v>79.13481898105066</v>
+        <v>197.7381876113653</v>
       </c>
       <c r="G29" t="n">
-        <v>91.736397999703</v>
+        <v>256.1875238587929</v>
       </c>
       <c r="H29" t="n">
-        <v>-12.60157901865234</v>
+        <v>-58.44933624742757</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="D31" t="n">
+        <v>20.58333333333333</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.86666666666667</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1794253337608642</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.4766783541068861</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.2972530203460219</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.01666666666667</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.05059730733317578</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0127297174998127</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.03786758983336308</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5766516264825126</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.4202840859765154</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1563675405059972</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>64.65921666666667</v>
+      </c>
+      <c r="D34" t="n">
+        <v>46.73333333333333</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.92588333333334</v>
+      </c>
+      <c r="F34" t="n">
+        <v>63.80717597571496</v>
+      </c>
+      <c r="G34" t="n">
+        <v>41.50209986904579</v>
+      </c>
+      <c r="H34" t="n">
+        <v>22.30507610666917</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>54.06666666666667</v>
+      </c>
+      <c r="D35" t="n">
+        <v>35.11666666666667</v>
+      </c>
+      <c r="E35" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="F35" t="n">
+        <v>54.00426203304914</v>
+      </c>
+      <c r="G35" t="n">
+        <v>32.50454485672611</v>
+      </c>
+      <c r="H35" t="n">
+        <v>21.49971717632302</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>176.7758166666667</v>
+      </c>
+      <c r="D36" t="n">
+        <v>220.4833333333333</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-43.70751666666658</v>
+      </c>
+      <c r="F36" t="n">
+        <v>206.2279801079839</v>
+      </c>
+      <c r="G36" t="n">
+        <v>250.8100111568945</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-44.58203104891058</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>65.98333333333333</v>
+      </c>
+      <c r="D38" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>30.58333333333334</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2402194601328752</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.4503679422720615</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.2101484821391863</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>30.53333333333333</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6.316666666666666</v>
+      </c>
+      <c r="E39" t="n">
+        <v>24.21666666666667</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.2158637009068103</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.06317093999191636</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1526927609148939</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>6.383333333333334</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-3.966666666666666</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.598015576168782</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.9160590253823516</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.3180434492135696</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>76.56666666666666</v>
+      </c>
+      <c r="D41" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10.76666666666667</v>
+      </c>
+      <c r="F41" t="n">
+        <v>71.21683905800106</v>
+      </c>
+      <c r="G41" t="n">
+        <v>59.81880415688165</v>
+      </c>
+      <c r="H41" t="n">
+        <v>11.39803490111941</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>59.98333333333333</v>
+      </c>
+      <c r="D42" t="n">
+        <v>46.88053333333333</v>
+      </c>
+      <c r="E42" t="n">
+        <v>13.10279999999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>57.6088865102048</v>
+      </c>
+      <c r="G42" t="n">
+        <v>44.25115544180538</v>
+      </c>
+      <c r="H42" t="n">
+        <v>13.35773106839942</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>171.2833333333333</v>
+      </c>
+      <c r="D43" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-12.1166666666667</v>
+      </c>
+      <c r="F43" t="n">
+        <v>195.5190827900918</v>
+      </c>
+      <c r="G43" t="n">
+        <v>219.3847649137591</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-23.86568212366731</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>65.98333333333333</v>
+      </c>
+      <c r="D45" t="n">
+        <v>20.63333333333333</v>
+      </c>
+      <c r="E45" t="n">
+        <v>45.35000000000001</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2402194601328752</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.4185697978984132</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.178350337765538</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>30.53333333333333</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="E46" t="n">
+        <v>27.86666666666666</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.2158637009068103</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.428265735708522</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.2124020348017117</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5.016666666666667</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5924866771054754</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.4666024413592124</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.125884235746263</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>75.51461666666667</v>
+      </c>
+      <c r="D48" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>32.41461666666667</v>
+      </c>
+      <c r="F48" t="n">
+        <v>70.78420748683264</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35.97418131675639</v>
+      </c>
+      <c r="H48" t="n">
+        <v>34.81002617007625</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>59.38333333333333</v>
+      </c>
+      <c r="D49" t="n">
+        <v>32.11666666666667</v>
+      </c>
+      <c r="E49" t="n">
+        <v>27.26666666666667</v>
+      </c>
+      <c r="F49" t="n">
+        <v>57.21717097154523</v>
+      </c>
+      <c r="G49" t="n">
+        <v>28.82664857731616</v>
+      </c>
+      <c r="H49" t="n">
+        <v>28.39052239422907</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>170.0333333333333</v>
+      </c>
+      <c r="D50" t="n">
+        <v>242.5133166666667</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-72.47998333333339</v>
+      </c>
+      <c r="F50" t="n">
+        <v>194.703693789026</v>
+      </c>
+      <c r="G50" t="n">
+        <v>258.0108718582774</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-63.30717806925142</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>58.16666666666666</v>
+      </c>
+      <c r="D52" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>22.76666666666666</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.3279316256974203</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.4503679422720615</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.1224363165746412</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>21.67998333333333</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6.316666666666666</v>
+      </c>
+      <c r="E53" t="n">
+        <v>15.36331666666666</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.07129119195051567</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.06317093999191636</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.008120251958599306</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8.083333333333334</v>
+      </c>
+      <c r="D54" t="n">
+        <v>10.68333333333333</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-2.599999999999996</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.5879855152386801</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.9301404042363888</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.3421548889977086</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>65.96666666666667</v>
+      </c>
+      <c r="D55" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.1333333333333258</v>
+      </c>
+      <c r="F55" t="n">
+        <v>64.43671090657982</v>
+      </c>
+      <c r="G55" t="n">
+        <v>59.92188649758575</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.514824408994066</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="D56" t="n">
+        <v>47.53333333333333</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7.266666666666666</v>
+      </c>
+      <c r="F56" t="n">
+        <v>54.47632725636674</v>
+      </c>
+      <c r="G56" t="n">
+        <v>44.51480319122793</v>
+      </c>
+      <c r="H56" t="n">
+        <v>9.961524065138811</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>177.1166666666667</v>
+      </c>
+      <c r="D57" t="n">
+        <v>185.7166666666667</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-8.599999999999994</v>
+      </c>
+      <c r="F57" t="n">
+        <v>206.4767797507066</v>
+      </c>
+      <c r="G57" t="n">
+        <v>220.2537734191309</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-13.7769936684243</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>58.16666666666666</v>
+      </c>
+      <c r="D59" t="n">
+        <v>24.31666666666667</v>
+      </c>
+      <c r="E59" t="n">
+        <v>33.84999999999999</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.3279316256974203</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.4423674542915821</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-0.1144358285941618</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>21.67998333333333</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="E60" t="n">
+        <v>19.01331666666666</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1014181648324159</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.428265735708522</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.3268475708761061</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5.683333333333334</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.316666666666666</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.5766516264825126</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.5110447249900278</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.06560690149248471</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>44.46666666666667</v>
+      </c>
+      <c r="E62" t="n">
+        <v>20.03333333333333</v>
+      </c>
+      <c r="F62" t="n">
+        <v>63.63085151532849</v>
+      </c>
+      <c r="G62" t="n">
+        <v>36.40661394018598</v>
+      </c>
+      <c r="H62" t="n">
+        <v>27.22423757514251</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>53.65215</v>
+      </c>
+      <c r="D63" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="E63" t="n">
+        <v>21.20215</v>
+      </c>
+      <c r="F63" t="n">
+        <v>53.72863846122127</v>
+      </c>
+      <c r="G63" t="n">
+        <v>29.04782298717766</v>
+      </c>
+      <c r="H63" t="n">
+        <v>24.68081547404361</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>176.5333333333333</v>
+      </c>
+      <c r="D64" t="n">
+        <v>243.15</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-66.6166666666667</v>
+      </c>
+      <c r="F64" t="n">
+        <v>206.0150800117203</v>
+      </c>
+      <c r="G64" t="n">
+        <v>258.1973335689265</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-52.18225355720622</v>
       </c>
     </row>
   </sheetData>
@@ -2423,19 +4402,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>32.67777777777778</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>32.67777777777778</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.06696925228687975</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2448,22 +4427,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.2625</v>
+        <v>52.09814814814815</v>
       </c>
       <c r="C3" t="n">
-        <v>3.420833333333333</v>
+        <v>25.94814814814815</v>
       </c>
       <c r="D3" t="n">
-        <v>10.84166666666667</v>
+        <v>26.15</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02250677479622844</v>
+        <v>0.2295208246077752</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04763835794280623</v>
+        <v>0.4396204495919946</v>
       </c>
     </row>
     <row r="4">
@@ -2473,22 +4452,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.666666666666667</v>
+        <v>27.5437</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.938888888888889</v>
       </c>
       <c r="D4" t="n">
-        <v>2.666666666666667</v>
+        <v>23.60481111111111</v>
       </c>
       <c r="E4" t="n">
-        <v>2.25</v>
+        <v>25.96666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04549276672691677</v>
+        <v>0.1045101972487693</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.1680554644000837</v>
       </c>
     </row>
     <row r="5">
@@ -2498,22 +4477,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2458333333333333</v>
+        <v>7.264814814814816</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3333333333333333</v>
+        <v>6.603703703703705</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08750000000000001</v>
+        <v>0.6611111111111113</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2.033333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02443272475899231</v>
+        <v>0.57010293011178</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01057419704744014</v>
+        <v>0.6106003735695792</v>
       </c>
     </row>
     <row r="6">
@@ -2523,22 +4502,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.80704166666667</v>
+        <v>70.11561111111112</v>
       </c>
       <c r="C6" t="n">
-        <v>7.924008333333334</v>
+        <v>51.77962962962962</v>
       </c>
       <c r="D6" t="n">
-        <v>5.883033333333334</v>
+        <v>18.33598148148148</v>
       </c>
       <c r="E6" t="n">
-        <v>3.474400000000002</v>
+        <v>20.03333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>13.50042967408626</v>
+        <v>67.38894504757143</v>
       </c>
       <c r="G6" t="n">
-        <v>7.840709038835927</v>
+        <v>45.59448232380238</v>
       </c>
     </row>
     <row r="7">
@@ -2548,22 +4527,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.8746875</v>
+        <v>57.24882777777778</v>
       </c>
       <c r="C7" t="n">
-        <v>6.416345833333333</v>
+        <v>37.70524444444445</v>
       </c>
       <c r="D7" t="n">
-        <v>4.458341666666666</v>
+        <v>19.54358333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>3.182708333333332</v>
+        <v>21.20215</v>
       </c>
       <c r="F7" t="n">
-        <v>10.84388300168103</v>
+        <v>55.93567203161024</v>
       </c>
       <c r="G7" t="n">
-        <v>6.502906813662789</v>
+        <v>34.98783135223046</v>
       </c>
     </row>
     <row r="8">
@@ -2573,22 +4552,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.10962916666666</v>
+        <v>170.6539907407407</v>
       </c>
       <c r="C8" t="n">
-        <v>40.26954166666667</v>
+        <v>215.1317037037037</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.159912499999997</v>
+        <v>-44.47771296296295</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.330283333333327</v>
+        <v>-49.58873333333329</v>
       </c>
       <c r="F8" t="n">
-        <v>40.32281880168853</v>
+        <v>199.6781796811159</v>
       </c>
       <c r="G8" t="n">
-        <v>50.29433563965681</v>
+        <v>242.3822786878695</v>
       </c>
     </row>
   </sheetData>
@@ -2659,28 +4638,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>36.5</v>
+        <v>46.77777777777778</v>
       </c>
       <c r="D2" t="n">
-        <v>1.290994448735806</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>35.75</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>36.5</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
-        <v>37.25</v>
+        <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -2690,28 +4669,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>73.96635833333336</v>
+        <v>417.6028703703703</v>
       </c>
       <c r="D3" t="n">
-        <v>72.69243097571685</v>
+        <v>17.90962916443039</v>
       </c>
       <c r="E3" t="n">
-        <v>11.71183333333333</v>
+        <v>394.6350333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>12.79469583333333</v>
+        <v>407.74795</v>
       </c>
       <c r="G3" t="n">
-        <v>64.93000833333335</v>
+        <v>410.7333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>126.1016708333334</v>
+        <v>420.64665</v>
       </c>
       <c r="I3" t="n">
-        <v>154.2935833333334</v>
+        <v>446.45</v>
       </c>
     </row>
     <row r="4">
@@ -2721,28 +4700,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>58.3640625</v>
+        <v>341.1073185185185</v>
       </c>
       <c r="D4" t="n">
-        <v>53.74624125705835</v>
+        <v>11.28173707475582</v>
       </c>
       <c r="E4" t="n">
-        <v>11.73173333333333</v>
+        <v>325.2655</v>
       </c>
       <c r="F4" t="n">
-        <v>13.45870833333334</v>
+        <v>329.75</v>
       </c>
       <c r="G4" t="n">
-        <v>51.96445833333333</v>
+        <v>346.04665</v>
       </c>
       <c r="H4" t="n">
-        <v>96.86981249999999</v>
+        <v>349.4259833333334</v>
       </c>
       <c r="I4" t="n">
-        <v>117.7956</v>
+        <v>352.7333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -2752,28 +4731,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>64.75956374373797</v>
+        <v>323.9738999645528</v>
       </c>
       <c r="D5" t="n">
-        <v>55.40644664848083</v>
+        <v>1.590930007385867</v>
       </c>
       <c r="E5" t="n">
-        <v>16.43424965629278</v>
+        <v>321.8611957625617</v>
       </c>
       <c r="F5" t="n">
-        <v>17.24138195894022</v>
+        <v>322.2735940834601</v>
       </c>
       <c r="G5" t="n">
-        <v>61.97557489747194</v>
+        <v>324.4297883243897</v>
       </c>
       <c r="H5" t="n">
-        <v>109.4937566822697</v>
+        <v>324.9350283808783</v>
       </c>
       <c r="I5" t="n">
-        <v>118.6528555237152</v>
+        <v>326.4659622430934</v>
       </c>
     </row>
     <row r="6">
@@ -2783,28 +4762,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>64.69616404714574</v>
+        <v>324.1828686514639</v>
       </c>
       <c r="D6" t="n">
-        <v>55.27043415422136</v>
+        <v>1.584579743162435</v>
       </c>
       <c r="E6" t="n">
-        <v>16.43868693033036</v>
+        <v>321.6269481176106</v>
       </c>
       <c r="F6" t="n">
-        <v>17.30661392491893</v>
+        <v>322.6469826189222</v>
       </c>
       <c r="G6" t="n">
-        <v>62.01270814721506</v>
+        <v>324.8843224200924</v>
       </c>
       <c r="H6" t="n">
-        <v>109.4022582694419</v>
+        <v>325.0350667285441</v>
       </c>
       <c r="I6" t="n">
-        <v>118.3205529638225</v>
+        <v>326.1341423944449</v>
       </c>
     </row>
     <row r="7">
@@ -2814,28 +4793,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>74.60565404058742</v>
+        <v>63.61263298859399</v>
       </c>
       <c r="D7" t="n">
-        <v>11.66135861698128</v>
+        <v>1.067753434132413</v>
       </c>
       <c r="E7" t="n">
-        <v>57.74313792935574</v>
+        <v>62.04817090988592</v>
       </c>
       <c r="F7" t="n">
-        <v>71.90472965881378</v>
+        <v>62.32616891116043</v>
       </c>
       <c r="G7" t="n">
-        <v>78.24321369160336</v>
+        <v>64.17415185678969</v>
       </c>
       <c r="H7" t="n">
-        <v>80.944138073377</v>
+        <v>64.4401967523076</v>
       </c>
       <c r="I7" t="n">
-        <v>84.19305084978724</v>
+        <v>64.64531488636605</v>
       </c>
     </row>
     <row r="8">
@@ -2845,28 +4824,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>74.87446735559691</v>
+        <v>62.43552184410132</v>
       </c>
       <c r="D8" t="n">
-        <v>9.794968801685402</v>
+        <v>1.938271345072508</v>
       </c>
       <c r="E8" t="n">
-        <v>61.22560386453947</v>
+        <v>59.70765591182442</v>
       </c>
       <c r="F8" t="n">
-        <v>71.72622740695616</v>
+        <v>60.09883681712126</v>
       </c>
       <c r="G8" t="n">
-        <v>77.09966690489205</v>
+        <v>63.51275377345894</v>
       </c>
       <c r="H8" t="n">
-        <v>80.24790685353281</v>
+        <v>63.75914065702941</v>
       </c>
       <c r="I8" t="n">
-        <v>84.07293174806406</v>
+        <v>64.28145295102571</v>
       </c>
     </row>
     <row r="9">
@@ -2876,28 +4855,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>15.60229583333336</v>
+        <v>76.49555185185183</v>
       </c>
       <c r="D9" t="n">
-        <v>32.53445497910606</v>
+        <v>15.97694689724951</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.091233333333292</v>
+        <v>61.7013</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9318458333333264</v>
+        <v>64.6321333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4493083333333354</v>
+        <v>68.89665000000002</v>
       </c>
       <c r="H9" t="n">
-        <v>16.08483333333335</v>
+        <v>83.36126666666661</v>
       </c>
       <c r="I9" t="n">
-        <v>64.39903333333341</v>
+        <v>105.0076166666667</v>
       </c>
     </row>
     <row r="10">
@@ -2907,28 +4886,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06339969659222344</v>
+        <v>-0.2089686869111915</v>
       </c>
       <c r="D10" t="n">
-        <v>0.184212222996786</v>
+        <v>0.524454154047782</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.08549686329243045</v>
+        <v>-0.7913196593714247</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.02470217135129094</v>
+        <v>-0.5722236421540288</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003396544884306962</v>
+        <v>-0.3733885354620838</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09149841282782134</v>
+        <v>0.3318198486484789</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3323025598927103</v>
+        <v>0.5505261860902237</v>
       </c>
     </row>
     <row r="11">
@@ -2938,28 +4917,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2688133150094867</v>
+        <v>1.177111144492669</v>
       </c>
       <c r="D11" t="n">
-        <v>3.598383924357832</v>
+        <v>2.2272532343591</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.482465935183733</v>
+        <v>-1.478482934639139</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.631345223837885</v>
+        <v>0.1587438012818865</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.11375960916638</v>
+        <v>0.6804186479323988</v>
       </c>
       <c r="H11" t="n">
-        <v>1.248772299662019</v>
+        <v>2.22733209403917</v>
       </c>
       <c r="I11" t="n">
-        <v>4.634731893478545</v>
+        <v>4.583605805398456</v>
       </c>
     </row>
     <row r="12">
@@ -2969,28 +4948,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>13.50833333333333</v>
+        <v>49.75481111111111</v>
       </c>
       <c r="D12" t="n">
-        <v>32.22319299303945</v>
+        <v>18.35066921922096</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.516666666666663</v>
+        <v>20.61666666666668</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.879166666666666</v>
+        <v>38.12998333333331</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>52.86331666666665</v>
       </c>
       <c r="H12" t="n">
-        <v>15.3875</v>
+        <v>56.61666666666666</v>
       </c>
       <c r="I12" t="n">
-        <v>61.55</v>
+        <v>76.78333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -3000,13 +4979,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>32.67777777777778</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>27.41411335628258</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3015,13 +4994,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="14">
@@ -3031,7 +5010,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -3062,13 +5041,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>32.67777777777778</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>27.41411335628258</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3077,13 +5056,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="16">
@@ -3093,13 +5072,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.06696925228687975</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.05120782777189859</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3108,13 +5087,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.08893599655368564</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
     </row>
     <row r="17">
@@ -3124,7 +5103,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -3155,13 +5134,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.06696925228687975</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.05120782777189859</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3170,13 +5149,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.08893599655368564</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
     </row>
     <row r="19">
@@ -3186,28 +5165,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>14.2625</v>
+        <v>52.09814814814815</v>
       </c>
       <c r="D19" t="n">
-        <v>28.525</v>
+        <v>16.88270697350061</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>14.51666666666667</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>51.31666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="H19" t="n">
-        <v>14.2625</v>
+        <v>65.98333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>57.05</v>
+        <v>65.98333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -3217,28 +5196,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>3.420833333333333</v>
+        <v>25.94814814814815</v>
       </c>
       <c r="D20" t="n">
-        <v>6.841666666666665</v>
+        <v>7.424744872367878</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>16.9</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>20.58333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>24.31666666666667</v>
       </c>
       <c r="H20" t="n">
-        <v>3.420833333333333</v>
+        <v>35.4</v>
       </c>
       <c r="I20" t="n">
-        <v>13.68333333333333</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="21">
@@ -3248,28 +5227,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>10.84166666666667</v>
+        <v>26.15000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>31.47363535123043</v>
+        <v>16.63770817550703</v>
       </c>
       <c r="E21" t="n">
-        <v>-13.68333333333333</v>
+        <v>-6.066666666666659</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.420833333333333</v>
+        <v>16.86666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H21" t="n">
-        <v>14.2625</v>
+        <v>33.84999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>57.05</v>
+        <v>49.08333333333334</v>
       </c>
     </row>
     <row r="22">
@@ -3279,28 +5258,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02250677479622844</v>
+        <v>0.2295208246077752</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04501354959245688</v>
+        <v>0.07452586510091193</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.08215844858586425</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.2137910036648912</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.2402194601328752</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02250677479622844</v>
+        <v>0.2402194601328752</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09002709918491375</v>
+        <v>0.3279316256974203</v>
       </c>
     </row>
     <row r="23">
@@ -3310,28 +5289,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04763835794280623</v>
+        <v>0.4396204495919946</v>
       </c>
       <c r="D23" t="n">
-        <v>0.09527671588561246</v>
+        <v>0.03869230654068306</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.3478638485950774</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.4423674542915821</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.4503679422720615</v>
       </c>
       <c r="H23" t="n">
-        <v>0.04763835794280623</v>
+        <v>0.4503679422720615</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1905534317712249</v>
+        <v>0.4766783541068861</v>
       </c>
     </row>
     <row r="24">
@@ -3341,28 +5320,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.02513158314657779</v>
+        <v>-0.2100996249842194</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1181652840468634</v>
+        <v>0.09422493644016433</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1905534317712249</v>
+        <v>-0.3945199055210218</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.04763835794280623</v>
+        <v>-0.2365769386071703</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.2101484821391863</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02250677479622844</v>
+        <v>-0.1224363165746412</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09002709918491375</v>
+        <v>-0.1076443884622022</v>
       </c>
     </row>
     <row r="25">
@@ -3372,28 +5351,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>2.666666666666667</v>
+        <v>27.54369999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>3.153481321404084</v>
+        <v>5.243821770949706</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>18.85</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>21.67998333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>2.25</v>
+        <v>30.53333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>4.916666666666667</v>
+        <v>30.53333333333333</v>
       </c>
       <c r="I25" t="n">
-        <v>6.166666666666667</v>
+        <v>32.28333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -3403,28 +5382,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3.938888888888888</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1.784793016321812</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>6.316666666666666</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>6.316666666666666</v>
       </c>
     </row>
     <row r="27">
@@ -3434,28 +5413,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>2.666666666666667</v>
+        <v>23.60481111111111</v>
       </c>
       <c r="D27" t="n">
-        <v>3.153481321404084</v>
+        <v>5.397805202264826</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>15.36331666666666</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>19.01331666666666</v>
       </c>
       <c r="G27" t="n">
-        <v>2.25</v>
+        <v>25.96666666666667</v>
       </c>
       <c r="H27" t="n">
-        <v>4.916666666666667</v>
+        <v>27.7</v>
       </c>
       <c r="I27" t="n">
-        <v>6.166666666666667</v>
+        <v>29.61666666666666</v>
       </c>
     </row>
     <row r="28">
@@ -3465,28 +5444,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>0.04549276672691677</v>
+        <v>0.1045101972487693</v>
       </c>
       <c r="D28" t="n">
-        <v>0.05801478780851648</v>
+        <v>0.08739743452855692</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.01643615657683831</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.0266289259127734</v>
       </c>
       <c r="G28" t="n">
-        <v>0.03041472177936588</v>
+        <v>0.07129119195051567</v>
       </c>
       <c r="H28" t="n">
-        <v>0.07590748850628265</v>
+        <v>0.2158637009068103</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1211416233489353</v>
+        <v>0.2158637009068103</v>
       </c>
     </row>
     <row r="29">
@@ -3496,28 +5475,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.1680554644000837</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.1963761407397156</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.0127297174998127</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.0127297174998127</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.06317093999191636</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.428265735708522</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.428265735708522</v>
       </c>
     </row>
     <row r="30">
@@ -3527,28 +5506,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04549276672691677</v>
+        <v>-0.06354526715131442</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05801478780851648</v>
+        <v>0.2074673230138593</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0.4016368097957486</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.2124020348017117</v>
       </c>
       <c r="G30" t="n">
-        <v>0.03041472177936588</v>
+        <v>0.00370643907702561</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07590748850628265</v>
+        <v>0.03786758983336308</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1211416233489353</v>
+        <v>0.2031339834069976</v>
       </c>
     </row>
     <row r="31">
@@ -3558,28 +5537,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2458333333333333</v>
+        <v>7.264814814814814</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3177976877989681</v>
+        <v>0.7860963877694629</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>6.383333333333334</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1583333333333334</v>
+        <v>7.716666666666667</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4041666666666667</v>
+        <v>8</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6666666666666666</v>
+        <v>8.083333333333334</v>
       </c>
     </row>
     <row r="32">
@@ -3589,28 +5568,28 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6.603703703703705</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.891303744970253</v>
+      </c>
+      <c r="E32" t="n">
         <v>4</v>
       </c>
-      <c r="C32" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.4714045207910317</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1666666666666667</v>
+        <v>5.683333333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>10.68333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -3620,28 +5599,28 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6611111111111113</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.841715542101676</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-3.966666666666666</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-2.300000000000002</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.316666666666666</v>
+      </c>
+      <c r="I33" t="n">
         <v>4</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.08750000000000001</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.4271730935485659</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-0.6833333333333333</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-0.1708333333333333</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -3651,28 +5630,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02443272475899231</v>
+        <v>0.5701029301117799</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03735922681288125</v>
+        <v>0.02961776324197001</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.5125712172728395</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.5621573347884641</v>
       </c>
       <c r="G34" t="n">
-        <v>0.009435627841696055</v>
+        <v>0.5766516264825126</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03386835260068836</v>
+        <v>0.5924866771054754</v>
       </c>
       <c r="I34" t="n">
-        <v>0.07885964335257711</v>
+        <v>0.598015576168782</v>
       </c>
     </row>
     <row r="35">
@@ -3682,28 +5661,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01057419704744014</v>
+        <v>0.6106003735695793</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01746450877072928</v>
+        <v>0.2313506776148299</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.4202840859765154</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.4202840859765154</v>
       </c>
       <c r="G35" t="n">
-        <v>0.002927525982392686</v>
+        <v>0.5110447249900278</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01350172302983283</v>
+        <v>0.8996597832386584</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03644173622497521</v>
+        <v>0.9301404042363888</v>
       </c>
     </row>
     <row r="36">
@@ -3713,28 +5692,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01385852771155216</v>
+        <v>-0.04049744345779919</v>
       </c>
       <c r="D36" t="n">
-        <v>0.04029126037919865</v>
+        <v>0.2302386633739837</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0175704805415831</v>
+        <v>-0.3677396628773797</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.004392620135395774</v>
+        <v>-0.3180434492135696</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.06560690149248471</v>
       </c>
       <c r="H36" t="n">
-        <v>0.01825114784694793</v>
+        <v>0.125884235746263</v>
       </c>
       <c r="I36" t="n">
-        <v>0.07300459138779174</v>
+        <v>0.17220259112896</v>
       </c>
     </row>
     <row r="37">
@@ -3744,28 +5723,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C37" t="n">
-        <v>13.80704166666667</v>
+        <v>70.11561111111112</v>
       </c>
       <c r="D37" t="n">
-        <v>14.69225439069915</v>
+        <v>4.785172457264616</v>
       </c>
       <c r="E37" t="n">
-        <v>1.5</v>
+        <v>64.5</v>
       </c>
       <c r="F37" t="n">
-        <v>2.15</v>
+        <v>65.96666666666667</v>
       </c>
       <c r="G37" t="n">
-        <v>10.79741666666667</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>22.45445833333333</v>
+        <v>75.51461666666667</v>
       </c>
       <c r="I37" t="n">
-        <v>32.13333333333333</v>
+        <v>76.56666666666666</v>
       </c>
     </row>
     <row r="38">
@@ -3775,28 +5754,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C38" t="n">
-        <v>7.924008333333334</v>
+        <v>51.77962962962962</v>
       </c>
       <c r="D38" t="n">
-        <v>7.872065217302445</v>
+        <v>10.08155555188181</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5833333333333334</v>
+        <v>43.1</v>
       </c>
       <c r="F38" t="n">
-        <v>1.408333333333333</v>
+        <v>44.46666666666667</v>
       </c>
       <c r="G38" t="n">
-        <v>7.873016666666667</v>
+        <v>46.73333333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>14.38869166666667</v>
+        <v>63.38333333333333</v>
       </c>
       <c r="I38" t="n">
-        <v>15.36666666666667</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3806,28 +5785,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C39" t="n">
-        <v>5.883033333333334</v>
+        <v>18.33598148148148</v>
       </c>
       <c r="D39" t="n">
-        <v>7.584561535997536</v>
+        <v>10.85617075824545</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.1833333333333329</v>
+        <v>-0.1333333333333258</v>
       </c>
       <c r="F39" t="n">
-        <v>1.291666666666667</v>
+        <v>10.76666666666667</v>
       </c>
       <c r="G39" t="n">
-        <v>3.474400000000002</v>
+        <v>20.03333333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>8.065766666666669</v>
+        <v>25.26666666666667</v>
       </c>
       <c r="I39" t="n">
-        <v>16.76666666666666</v>
+        <v>32.41461666666667</v>
       </c>
     </row>
     <row r="40">
@@ -3837,28 +5816,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>13.50042967408626</v>
+        <v>67.38894504757143</v>
       </c>
       <c r="D40" t="n">
-        <v>12.79475124204572</v>
+        <v>3.057443073736734</v>
       </c>
       <c r="E40" t="n">
-        <v>2.145589159808596</v>
+        <v>63.63085151532849</v>
       </c>
       <c r="F40" t="n">
-        <v>2.837615267342489</v>
+        <v>64.43671090657982</v>
       </c>
       <c r="G40" t="n">
-        <v>12.31606038683624</v>
+        <v>67.23521804769611</v>
       </c>
       <c r="H40" t="n">
-        <v>22.97887479358001</v>
+        <v>70.78420748683264</v>
       </c>
       <c r="I40" t="n">
-        <v>27.22400876286396</v>
+        <v>71.21683905800106</v>
       </c>
     </row>
     <row r="41">
@@ -3868,28 +5847,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C41" t="n">
-        <v>7.840709038835927</v>
+        <v>45.59448232380239</v>
       </c>
       <c r="D41" t="n">
-        <v>7.402625993424762</v>
+        <v>10.57224109762126</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6703253541496691</v>
+        <v>35.97418131675639</v>
       </c>
       <c r="F41" t="n">
-        <v>1.933158962389719</v>
+        <v>36.40661394018598</v>
       </c>
       <c r="G41" t="n">
-        <v>7.672195759117699</v>
+        <v>41.50209986904579</v>
       </c>
       <c r="H41" t="n">
-        <v>13.57974583556391</v>
+        <v>58.37602971556508</v>
       </c>
       <c r="I41" t="n">
-        <v>15.34811928295864</v>
+        <v>59.92188649758575</v>
       </c>
     </row>
     <row r="42">
@@ -3899,28 +5878,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C42" t="n">
-        <v>5.659720635250334</v>
+        <v>21.79446272376905</v>
       </c>
       <c r="D42" t="n">
-        <v>6.295443660934826</v>
+        <v>10.84276940608675</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.2085143386611401</v>
+        <v>4.514824408994066</v>
       </c>
       <c r="F42" t="n">
-        <v>1.746345377112803</v>
+        <v>11.39803490111941</v>
       </c>
       <c r="G42" t="n">
-        <v>4.306838068282088</v>
+        <v>26.46618830560372</v>
       </c>
       <c r="H42" t="n">
-        <v>8.220213326419618</v>
+        <v>29.46875227164809</v>
       </c>
       <c r="I42" t="n">
-        <v>14.2337207430983</v>
+        <v>34.81002617007625</v>
       </c>
     </row>
     <row r="43">
@@ -3930,28 +5909,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C43" t="n">
-        <v>10.8746875</v>
+        <v>57.24882777777778</v>
       </c>
       <c r="D43" t="n">
-        <v>11.66193030532169</v>
+        <v>2.448606383429607</v>
       </c>
       <c r="E43" t="n">
-        <v>1.233333333333333</v>
+        <v>53.65215</v>
       </c>
       <c r="F43" t="n">
-        <v>1.570833333333333</v>
+        <v>54.8</v>
       </c>
       <c r="G43" t="n">
-        <v>8.407708333333332</v>
+        <v>57.93333333333333</v>
       </c>
       <c r="H43" t="n">
-        <v>17.7115625</v>
+        <v>59.38333333333333</v>
       </c>
       <c r="I43" t="n">
-        <v>25.45</v>
+        <v>59.98333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -3961,28 +5940,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
-        <v>6.416345833333333</v>
+        <v>37.70524444444445</v>
       </c>
       <c r="D44" t="n">
-        <v>6.082858873786467</v>
+        <v>6.600739123933184</v>
       </c>
       <c r="E44" t="n">
-        <v>0.35</v>
+        <v>32.11666666666667</v>
       </c>
       <c r="F44" t="n">
-        <v>1.7615375</v>
+        <v>32.45</v>
       </c>
       <c r="G44" t="n">
-        <v>6.166024999999999</v>
+        <v>34.78333333333333</v>
       </c>
       <c r="H44" t="n">
-        <v>10.82083333333333</v>
+        <v>44.56666666666667</v>
       </c>
       <c r="I44" t="n">
-        <v>12.98333333333333</v>
+        <v>47.53333333333333</v>
       </c>
     </row>
     <row r="45">
@@ -3992,28 +5971,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C45" t="n">
-        <v>4.458341666666666</v>
+        <v>19.54358333333333</v>
       </c>
       <c r="D45" t="n">
-        <v>5.888056032978967</v>
+        <v>6.901666026432798</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.9987166666666671</v>
+        <v>7.266666666666666</v>
       </c>
       <c r="F45" t="n">
-        <v>0.750320833333333</v>
+        <v>13.36666666666666</v>
       </c>
       <c r="G45" t="n">
-        <v>3.182708333333332</v>
+        <v>21.20215</v>
       </c>
       <c r="H45" t="n">
-        <v>6.890729166666665</v>
+        <v>24.81666666666667</v>
       </c>
       <c r="I45" t="n">
-        <v>12.46666666666667</v>
+        <v>27.26666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -4023,28 +6002,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>10.84388300168103</v>
+        <v>55.93567203161024</v>
       </c>
       <c r="D46" t="n">
-        <v>10.38103054749051</v>
+        <v>1.489956507318155</v>
       </c>
       <c r="E46" t="n">
-        <v>1.726998909362367</v>
+        <v>53.72863846122127</v>
       </c>
       <c r="F46" t="n">
-        <v>2.0867476533311</v>
+        <v>54.47632725636674</v>
       </c>
       <c r="G46" t="n">
-        <v>9.965415164307954</v>
+        <v>56.31975683439349</v>
       </c>
       <c r="H46" t="n">
-        <v>18.72255051265788</v>
+        <v>57.21717097154523</v>
       </c>
       <c r="I46" t="n">
-        <v>21.71770276874582</v>
+        <v>57.6088865102048</v>
       </c>
     </row>
     <row r="47">
@@ -4054,28 +6033,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>6.50290681366279</v>
+        <v>34.98783135223046</v>
       </c>
       <c r="D47" t="n">
-        <v>5.668633633187604</v>
+        <v>6.85293532441322</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4473149966220811</v>
+        <v>28.82664857731616</v>
       </c>
       <c r="F47" t="n">
-        <v>2.283736936185459</v>
+        <v>29.04782298717766</v>
       </c>
       <c r="G47" t="n">
-        <v>7.047735763821267</v>
+        <v>32.23439151995442</v>
       </c>
       <c r="H47" t="n">
-        <v>11.2669056412986</v>
+        <v>42.97209112540976</v>
       </c>
       <c r="I47" t="n">
-        <v>11.46884073038654</v>
+        <v>44.51480319122793</v>
       </c>
     </row>
     <row r="48">
@@ -4085,28 +6064,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>4.340976188018235</v>
+        <v>20.94784067937978</v>
       </c>
       <c r="D48" t="n">
-        <v>5.056168114972037</v>
+        <v>6.888534507214233</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.168878673344218</v>
+        <v>9.961524065138811</v>
       </c>
       <c r="F48" t="n">
-        <v>1.027292010187893</v>
+        <v>13.35773106839942</v>
       </c>
       <c r="G48" t="n">
-        <v>4.141960693528938</v>
+        <v>24.68081547404361</v>
       </c>
       <c r="H48" t="n">
-        <v>7.45564487135928</v>
+        <v>25.15553619880751</v>
       </c>
       <c r="I48" t="n">
-        <v>10.24886203835928</v>
+        <v>28.39052239422907</v>
       </c>
     </row>
     <row r="49">
@@ -4116,28 +6095,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>32.10962916666666</v>
+        <v>170.6539907407407</v>
       </c>
       <c r="D49" t="n">
-        <v>26.74044709397405</v>
+        <v>5.310495212032644</v>
       </c>
       <c r="E49" t="n">
-        <v>8.9785</v>
+        <v>164.5166666666667</v>
       </c>
       <c r="F49" t="n">
-        <v>9.073862500000001</v>
+        <v>164.6</v>
       </c>
       <c r="G49" t="n">
-        <v>30.696675</v>
+        <v>170.4267666666667</v>
       </c>
       <c r="H49" t="n">
-        <v>53.73244166666667</v>
+        <v>176.5333333333333</v>
       </c>
       <c r="I49" t="n">
-        <v>58.06666666666667</v>
+        <v>177.1166666666667</v>
       </c>
     </row>
     <row r="50">
@@ -4147,28 +6126,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>40.26954166666667</v>
+        <v>215.1317037037037</v>
       </c>
       <c r="D50" t="n">
-        <v>34.76552337099186</v>
+        <v>25.56723221757926</v>
       </c>
       <c r="E50" t="n">
-        <v>7.81635</v>
+        <v>181.75905</v>
       </c>
       <c r="F50" t="n">
-        <v>11.7798625</v>
+        <v>185.7166666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>38.91644166666666</v>
+        <v>220.0155</v>
       </c>
       <c r="H50" t="n">
-        <v>67.40612083333333</v>
+        <v>240.5093166666666</v>
       </c>
       <c r="I50" t="n">
-        <v>75.42893333333333</v>
+        <v>243.15</v>
       </c>
     </row>
     <row r="51">
@@ -4178,28 +6157,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C51" t="n">
-        <v>-8.159912499999997</v>
+        <v>-44.47771296296295</v>
       </c>
       <c r="D51" t="n">
-        <v>10.50267174939905</v>
+        <v>26.13111439888781</v>
       </c>
       <c r="E51" t="n">
-        <v>-23.14123333333333</v>
+        <v>-75.9093166666666</v>
       </c>
       <c r="F51" t="n">
-        <v>-10.78419583333333</v>
+        <v>-66.6166666666667</v>
       </c>
       <c r="G51" t="n">
-        <v>-5.330283333333327</v>
+        <v>-49.58873333333329</v>
       </c>
       <c r="H51" t="n">
-        <v>-2.705999999999997</v>
+        <v>-17.15905000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>1.16215</v>
+        <v>-8.599999999999994</v>
       </c>
     </row>
     <row r="52">
@@ -4209,28 +6188,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>40.32281880168853</v>
+        <v>199.6781796811159</v>
       </c>
       <c r="D52" t="n">
-        <v>33.44744516550085</v>
+        <v>5.057155927105585</v>
       </c>
       <c r="E52" t="n">
-        <v>12.23547152198156</v>
+        <v>194.703693789026</v>
       </c>
       <c r="F52" t="n">
-        <v>12.48011407083675</v>
+        <v>195.5190827900918</v>
       </c>
       <c r="G52" t="n">
-        <v>34.96049235186094</v>
+        <v>197.7381876113653</v>
       </c>
       <c r="H52" t="n">
-        <v>62.80319708271272</v>
+        <v>206.0150800117203</v>
       </c>
       <c r="I52" t="n">
-        <v>79.13481898105066</v>
+        <v>206.4767797507066</v>
       </c>
     </row>
     <row r="53">
@@ -4240,28 +6219,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C53" t="n">
-        <v>50.29433563965681</v>
+        <v>242.3822786878695</v>
       </c>
       <c r="D53" t="n">
-        <v>42.35243702433503</v>
+        <v>17.46572372752432</v>
       </c>
       <c r="E53" t="n">
-        <v>11.18870584915403</v>
+        <v>218.8656286111331</v>
       </c>
       <c r="F53" t="n">
-        <v>15.15588839154604</v>
+        <v>220.2537734191309</v>
       </c>
       <c r="G53" t="n">
-        <v>49.12611935488511</v>
+        <v>250.5176976874725</v>
       </c>
       <c r="H53" t="n">
-        <v>84.26456660299587</v>
+        <v>256.1875238587929</v>
       </c>
       <c r="I53" t="n">
-        <v>91.736397999703</v>
+        <v>258.1973335689265</v>
       </c>
     </row>
     <row r="54">
@@ -4271,28 +6250,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C54" t="n">
-        <v>-9.971516837968284</v>
+        <v>-42.70409900675358</v>
       </c>
       <c r="D54" t="n">
-        <v>11.21064910658513</v>
+        <v>18.2512641640792</v>
       </c>
       <c r="E54" t="n">
-        <v>-24.41463302082675</v>
+        <v>-63.30717806925142</v>
       </c>
       <c r="F54" t="n">
-        <v>-15.55484251919595</v>
+        <v>-55.4972590606838</v>
       </c>
       <c r="G54" t="n">
-        <v>-8.422195034507084</v>
+        <v>-51.54871628544322</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.838869353279421</v>
+        <v>-23.86568212366731</v>
       </c>
       <c r="I54" t="n">
-        <v>1.37295573796778</v>
+        <v>-13.7769936684243</v>
       </c>
     </row>
   </sheetData>
@@ -4348,67 +6327,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>73.96635833333336</v>
+        <v>417.6028703703703</v>
       </c>
       <c r="D2" t="n">
-        <v>58.3640625</v>
+        <v>341.1073185185185</v>
       </c>
       <c r="E2" t="n">
-        <v>15.60229583333336</v>
+        <v>76.49555185185181</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4493083333333354</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>16_clustered_phase_heatmap.png</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Constant phase dimensions omitted: charging_refueling_time_diff_min</t>
-        </is>
+        <v>68.89665000000002</v>
       </c>
     </row>
   </sheetData>
